--- a/tests/traces/perf_model/normalization/normalization_layer_test_perf_report.xlsx
+++ b/tests/traces/perf_model/normalization/normalization_layer_test_perf_report.xlsx
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,25 +700,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -734,20 +744,26 @@
         <v>171.4462890625</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'NORM_bwd'}</t>
-        </is>
+        <v>171.4462890625</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1714462890625</v>
       </c>
       <c r="E2" t="n">
         <v>0.1714462890625</v>
       </c>
       <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{'NORM_bwd'}</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>17.28304516936914</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>17.28304516936914</v>
       </c>
     </row>
@@ -761,20 +777,26 @@
         <v>104.5361328125</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>104.5361328125</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1045361328125</v>
       </c>
       <c r="E3" t="n">
         <v>0.1045361328125</v>
       </c>
       <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>10.53800998032091</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>27.82105514969005</v>
       </c>
     </row>
@@ -788,20 +810,26 @@
         <v>100.2841796875</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>{'NORM_bwd'}</t>
-        </is>
+        <v>100.2841796875</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1002841796875</v>
       </c>
       <c r="E4" t="n">
         <v>0.1002841796875</v>
       </c>
       <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{'NORM_bwd'}</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>10.1093818757451</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>37.93043702543515</v>
       </c>
     </row>
@@ -815,20 +843,26 @@
         <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.083</v>
       </c>
       <c r="E5" t="n">
         <v>0.083</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>8.367009615091176</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>46.29744664052633</v>
       </c>
     </row>
@@ -842,20 +876,26 @@
         <v>80.7080078125</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>80.7080078125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0807080078125</v>
       </c>
       <c r="E6" t="n">
         <v>0.0807080078125</v>
       </c>
       <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>8.135959968458327</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>54.43340660898465</v>
       </c>
     </row>
@@ -869,20 +909,26 @@
         <v>78.42236328125</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>78.42236328125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.07842236328125</v>
       </c>
       <c r="E7" t="n">
         <v>0.07842236328125</v>
       </c>
       <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>7.905550212197493</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>62.33895682118215</v>
       </c>
     </row>
@@ -896,20 +942,26 @@
         <v>66.76806640625</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'NORM_bwd'}</t>
-        </is>
+        <v>66.76806640625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06676806640625001</v>
       </c>
       <c r="E8" t="n">
         <v>0.06676806640625001</v>
       </c>
       <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{'NORM_bwd'}</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>6.730711489182408</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>69.06966831036456</v>
       </c>
     </row>
@@ -923,20 +975,26 @@
         <v>63.4287109375</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>63.4287109375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06342871093749999</v>
       </c>
       <c r="E9" t="n">
         <v>0.06342871093749999</v>
       </c>
       <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>6.394079931167484</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>75.46374824153204</v>
       </c>
     </row>
@@ -950,20 +1008,26 @@
         <v>53.794921875</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'NORM_bwd'}</t>
-        </is>
+        <v>53.794921875</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.053794921875</v>
       </c>
       <c r="E10" t="n">
         <v>0.053794921875</v>
       </c>
       <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{'NORM_bwd'}</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>5.422923235797633</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>80.88667147732968</v>
       </c>
     </row>
@@ -977,20 +1041,26 @@
         <v>31.32275390625</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>31.32275390625</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.03132275390625</v>
       </c>
       <c r="E11" t="n">
         <v>0.03132275390625</v>
       </c>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>3.157563651864197</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>84.04423512919388</v>
       </c>
     </row>
@@ -1004,20 +1074,26 @@
         <v>28.7177734375</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>{'NORM_bwd'}</t>
-        </is>
+        <v>28.7177734375</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0287177734375</v>
       </c>
       <c r="E12" t="n">
         <v>0.0287177734375</v>
       </c>
       <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{'NORM_bwd'}</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>2.894962487657499</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>86.93919761685137</v>
       </c>
     </row>
@@ -1031,20 +1107,26 @@
         <v>27.236328125</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>{'NORM_fwd'}</t>
-        </is>
+        <v>27.236328125</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.027236328125</v>
       </c>
       <c r="E13" t="n">
         <v>0.027236328125</v>
       </c>
       <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{'NORM_fwd'}</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>2.745621919297026</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>89.6848195361484</v>
       </c>
     </row>
@@ -1058,20 +1140,26 @@
         <v>25.99169921875</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>25.99169921875</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.02599169921875</v>
       </c>
       <c r="E14" t="n">
         <v>0.02599169921875</v>
       </c>
       <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>2.620154184046254</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>92.30497372019465</v>
       </c>
     </row>
@@ -1085,20 +1173,26 @@
         <v>20.66455078125</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>20.66455078125</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02066455078125</v>
       </c>
       <c r="E15" t="n">
         <v>0.02066455078125</v>
       </c>
       <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>2.083138494918778</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>94.38811221511344</v>
       </c>
     </row>
@@ -1112,20 +1206,26 @@
         <v>17.6201171875</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>17.6201171875</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0176201171875</v>
       </c>
       <c r="E16" t="n">
         <v>0.0176201171875</v>
       </c>
       <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>1.776237228034286</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>96.16434944314773</v>
       </c>
     </row>
@@ -1139,20 +1239,26 @@
         <v>13.37646484375</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>13.37646484375</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01337646484375</v>
       </c>
       <c r="E17" t="n">
         <v>0.01337646484375</v>
       </c>
       <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>1.348445903175727</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>97.51279534632346</v>
       </c>
     </row>
@@ -1166,20 +1272,26 @@
         <v>13.33935546875</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>13.33935546875</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01333935546875</v>
       </c>
       <c r="E18" t="n">
         <v>0.01333935546875</v>
       </c>
       <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>1.344705005616269</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>98.85750035193972</v>
       </c>
     </row>
@@ -1193,20 +1305,26 @@
         <v>11.33349609375</v>
       </c>
       <c r="C19" t="n">
+        <v>42.65625</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01133349609375</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04265625</v>
+      </c>
+      <c r="F19" t="n">
         <v>3</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{'elementwise'}</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.01133349609375</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>1.142499648060295</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1221,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,50 +1400,80 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1384,37 +1532,55 @@
         <v>32.6064453125</v>
       </c>
       <c r="L2" t="n">
+        <v>32.6064453125</v>
+      </c>
+      <c r="M2" t="n">
         <v>32.2861328125</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>32.2861328125</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.5902431727220115</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>0.5902431727220115</v>
+      </c>
+      <c r="Q2" t="n">
         <v>32.24560546875</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
+        <v>32.24560546875</v>
+      </c>
+      <c r="S2" t="n">
         <v>33.28759765625</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>33.28759765625</v>
+      </c>
+      <c r="U2" t="n">
         <v>97.8193359375</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
+        <v>97.8193359375</v>
+      </c>
+      <c r="W2" t="n">
         <v>152</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, false&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(84.883), 'mean_duration_us': np.float64(28.29433333333333), 'median_duration_us': np.float64(28.201), 'std_dev_duration_us': np.float64(0.4143543840187468), 'min_duration_us': np.float64(27.84), 'max_duration_us': np.float64(28.842)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleCUDAKernel&lt;float, float, false&gt;(long, long, float const*, float const*, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.936999999999998), 'mean_duration_us': np.float64(4.312333333333332), 'median_duration_us': np.float64(4.406), 'std_dev_duration_us': np.float64(0.16157626338323602), 'min_duration_us': np.float64(4.085), 'max_duration_us': np.float64(4.446)}]</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(28.29)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleC...', 'stream': 0, 'mean_duration_us': np.float64(4.31)}]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>9.860907522058989</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>9.860907522058989</v>
       </c>
     </row>
@@ -1471,37 +1637,55 @@
         <v>24.54231770833333</v>
       </c>
       <c r="L3" t="n">
+        <v>24.54231770833333</v>
+      </c>
+      <c r="M3" t="n">
         <v>24.59619140625</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>24.59619140625</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.8028704426605566</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
+        <v>0.8028704426605566</v>
+      </c>
+      <c r="Q3" t="n">
         <v>23.7138671875</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
+        <v>23.7138671875</v>
+      </c>
+      <c r="S3" t="n">
         <v>25.31689453125</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>25.31689453125</v>
+      </c>
+      <c r="U3" t="n">
         <v>73.626953125</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
+        <v>73.626953125</v>
+      </c>
+      <c r="W3" t="n">
         <v>55</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, false&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(73.62700000000001), 'mean_duration_us': np.float64(24.542333333333335), 'median_duration_us': np.float64(24.596), 'std_dev_duration_us': np.float64(0.6555213362067043), 'min_duration_us': np.float64(23.714), 'max_duration_us': np.float64(25.317)}]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(24.54)}]</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>7.422137647310147</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
         <v>17.28304516936914</v>
       </c>
     </row>
@@ -1558,37 +1742,55 @@
         <v>21.78857421875</v>
       </c>
       <c r="L4" t="n">
+        <v>21.78857421875</v>
+      </c>
+      <c r="M4" t="n">
         <v>14.2177734375</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>14.2177734375</v>
+      </c>
+      <c r="O4" t="n">
         <v>14.41545950056331</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>14.41545950056331</v>
+      </c>
+      <c r="Q4" t="n">
         <v>12.73583984375</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
+        <v>12.73583984375</v>
+      </c>
+      <c r="S4" t="n">
         <v>38.412109375</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>38.412109375</v>
+      </c>
+      <c r="U4" t="n">
         <v>65.36572265625</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>65.36572265625</v>
+      </c>
+      <c r="W4" t="n">
         <v>803</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(37.091), 'mean_duration_us': np.float64(12.363666666666667), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(12.076039232942046), 'min_duration_us': np.float64(3.685), 'max_duration_us': np.float64(29.441)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(15.74), 'mean_duration_us': np.float64(5.246666666666667), 'median_duration_us': np.float64(4.926), 'std_dev_duration_us': np.float64(0.6308519812303217), 'min_duration_us': np.float64(4.686), 'max_duration_us': np.float64(6.128)}, {'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.535), 'mean_duration_us': np.float64(4.178333333333334), 'median_duration_us': np.float64(4.125), 'std_dev_duration_us': np.float64(0.07542472332656514), 'min_duration_us': np.float64(4.125), 'max_duration_us': np.float64(4.285)}]</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(12.36)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(5.25)}, {'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'mean_duration_us': np.float64(4.18)}]</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="Z4" t="n">
         <v>6.589344939303937</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
         <v>23.87239010867307</v>
       </c>
     </row>
@@ -1645,37 +1847,55 @@
         <v>19.42350260416667</v>
       </c>
       <c r="L5" t="n">
+        <v>19.42350260416667</v>
+      </c>
+      <c r="M5" t="n">
         <v>20.10498046875</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>20.10498046875</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.991555167180243</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>1.991555167180243</v>
+      </c>
+      <c r="Q5" t="n">
         <v>17.1806640625</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
+        <v>17.1806640625</v>
+      </c>
+      <c r="S5" t="n">
         <v>20.98486328125</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>20.98486328125</v>
+      </c>
+      <c r="U5" t="n">
         <v>58.2705078125</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
+        <v>58.2705078125</v>
+      </c>
+      <c r="W5" t="n">
         <v>123</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.216000000000001), 'mean_duration_us': np.float64(4.405333333333334), 'median_duration_us': np.float64(4.405), 'std_dev_duration_us': np.float64(0.1963675691712412), 'min_duration_us': np.float64(4.165), 'max_duration_us': np.float64(4.646)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(6.327), 'mean_duration_us': np.float64(2.109), 'median_duration_us': np.float64(2.122), 'std_dev_duration_us': np.float64(0.24552936009094037), 'min_duration_us': np.float64(1.802), 'max_duration_us': np.float64(2.403)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.370999999999999), 'mean_duration_us': np.float64(3.1236666666666664), 'median_duration_us': np.float64(2.723), 'std_dev_duration_us': np.float64(0.624051992135983), 'min_duration_us': np.float64(2.643), 'max_duration_us': np.float64(4.005)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.942), 'mean_duration_us': np.float64(5.647333333333333), 'median_duration_us': np.float64(4.726), 'std_dev_duration_us': np.float64(1.4759235150312575), 'min_duration_us': np.float64(4.486), 'max_duration_us': np.float64(7.73)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKernel1&lt;float&gt;(long, long, long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.415), 'mean_duration_us': np.float64(4.138333333333333), 'median_duration_us': np.float64(4.085), 'std_dev_duration_us': np.float64(0.1359738536958077), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(4.325)}]</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.41)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(2.11)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(3.12)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.65)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKer...', 'stream': 0, 'mean_duration_us': np.float64(4.14)}]</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="Z5" t="n">
         <v>5.874095170402806</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>29.74648527907588</v>
       </c>
     </row>
@@ -1732,37 +1952,55 @@
         <v>17.72981770833333</v>
       </c>
       <c r="L6" t="n">
+        <v>17.72981770833333</v>
+      </c>
+      <c r="M6" t="n">
         <v>17.6630859375</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>17.6630859375</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.463543802533565</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
+        <v>1.463543802533565</v>
+      </c>
+      <c r="Q6" t="n">
         <v>16.30078125</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
+        <v>16.30078125</v>
+      </c>
+      <c r="S6" t="n">
         <v>19.2255859375</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>19.2255859375</v>
+      </c>
+      <c r="U6" t="n">
         <v>53.189453125</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
+        <v>53.189453125</v>
+      </c>
+      <c r="W6" t="n">
         <v>922</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(32.966), 'mean_duration_us': np.float64(10.988666666666667), 'median_duration_us': np.float64(11.376), 'std_dev_duration_us': np.float64(0.5762877367735286), 'min_duration_us': np.float64(10.174), 'max_duration_us': np.float64(11.416)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_kernel_for_multi_outputs&lt;3, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.530000000000001), 'mean_duration_us': np.float64(3.176666666666667), 'median_duration_us': np.float64(3.644), 'std_dev_duration_us': np.float64(0.8672271264720037), 'min_duration_us': np.float64(1.961), 'max_duration_us': np.float64(3.925)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(10.693999999999999), 'mean_duration_us': np.float64(3.564666666666666), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.7857575255057304), 'min_duration_us': np.float64(2.483), 'max_duration_us': np.float64(4.326)}]</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(10.99)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_ker...', 'stream': 0, 'mean_duration_us': np.float64(3.18)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.56)}]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
         <v>5.361887538774895</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AA6" t="n">
         <v>35.10837281785078</v>
       </c>
     </row>
@@ -1819,37 +2057,55 @@
         <v>17.11555989583333</v>
       </c>
       <c r="L7" t="n">
+        <v>17.11555989583333</v>
+      </c>
+      <c r="M7" t="n">
         <v>16.82177734375</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>16.82177734375</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.228537781176482</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
+        <v>1.228537781176482</v>
+      </c>
+      <c r="Q7" t="n">
         <v>16.060546875</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
+        <v>16.060546875</v>
+      </c>
+      <c r="S7" t="n">
         <v>18.46435546875</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>18.46435546875</v>
+      </c>
+      <c r="U7" t="n">
         <v>51.3466796875</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
+        <v>51.3466796875</v>
+      </c>
+      <c r="W7" t="n">
         <v>960</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.587), 'mean_duration_us': np.float64(6.862333333333333), 'median_duration_us': np.float64(6.568), 'std_dev_duration_us': np.float64(0.8121807406948011), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(7.971)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.865000000000002), 'mean_duration_us': np.float64(6.288333333333334), 'median_duration_us': np.float64(6.369), 'std_dev_duration_us': np.float64(0.17297462883967188), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(6.448)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.895), 'mean_duration_us': np.float64(3.965), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(0.06531972647421815), 'min_duration_us': np.float64(3.885), 'max_duration_us': np.float64(4.045)}]</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(6.86)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(6.29)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.96)}]</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="Z7" t="n">
         <v>5.176122441546014</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AA7" t="n">
         <v>40.28449525939679</v>
       </c>
     </row>
@@ -1906,37 +2162,55 @@
         <v>16.39501953125</v>
       </c>
       <c r="L8" t="n">
+        <v>16.39501953125</v>
+      </c>
+      <c r="M8" t="n">
         <v>16.14111328125</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>16.14111328125</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.888479895343345</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
+        <v>0.888479895343345</v>
+      </c>
+      <c r="Q8" t="n">
         <v>15.6611328125</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
+        <v>15.6611328125</v>
+      </c>
+      <c r="S8" t="n">
         <v>17.3828125</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>17.3828125</v>
+      </c>
+      <c r="U8" t="n">
         <v>49.18505859375</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
+        <v>49.18505859375</v>
+      </c>
+      <c r="W8" t="n">
         <v>71</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, true&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.782999999999998), 'mean_duration_us': np.float64(5.594333333333332), 'median_duration_us': np.float64(5.528), 'std_dev_duration_us': np.float64(0.2178077643754286), 'min_duration_us': np.float64(5.367), 'max_duration_us': np.float64(5.888)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, long, long, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.707), 'mean_duration_us': np.float64(6.902333333333334), 'median_duration_us': np.float64(6.889), 'std_dev_duration_us': np.float64(0.5071320231348923), 'min_duration_us': np.float64(6.288), 'max_duration_us': np.float64(7.53)}, {'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, int, long, long, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.695), 'mean_duration_us': np.float64(3.8983333333333334), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.04988876515698577), 'min_duration_us': np.float64(3.845), 'max_duration_us': np.float64(3.965)}]</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.59)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBe...', 'stream': 0, 'mean_duration_us': np.float64(6.9)}, {'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;f...', 'stream': 0, 'mean_duration_us': np.float64(3.9)}]</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="Z8" t="n">
         <v>4.958215158707579</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AA8" t="n">
         <v>45.24271041810437</v>
       </c>
     </row>
@@ -1993,37 +2267,55 @@
         <v>15.94108072916667</v>
       </c>
       <c r="L9" t="n">
+        <v>15.94108072916667</v>
+      </c>
+      <c r="M9" t="n">
         <v>17.02197265625</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>17.02197265625</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.936634842645699</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>2.936634842645699</v>
+      </c>
+      <c r="Q9" t="n">
         <v>12.6171875</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
+        <v>12.6171875</v>
+      </c>
+      <c r="S9" t="n">
         <v>18.18408203125</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>18.18408203125</v>
+      </c>
+      <c r="U9" t="n">
         <v>47.8232421875</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
+        <v>47.8232421875</v>
+      </c>
+      <c r="W9" t="n">
         <v>821</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.869999999999997), 'mean_duration_us': np.float64(7.289999999999999), 'median_duration_us': np.float64(7.17), 'std_dev_duration_us': np.float64(0.5463338417732021), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(8.011)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.296), 'mean_duration_us': np.float64(4.0986666666666665), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.4510511898467109), 'min_duration_us': np.float64(2.123), 'max_duration_us': np.float64(5.567)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.657), 'mean_duration_us': np.float64(4.552333333333333), 'median_duration_us': np.float64(4.285), 'std_dev_duration_us': np.float64(0.7437568300339985), 'min_duration_us': np.float64(3.805), 'max_duration_us': np.float64(5.567)}]</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.29)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKe...', 'stream': 0, 'mean_duration_us': np.float64(4.1)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.55)}]</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
         <v>4.820934062742728</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AA9" t="n">
         <v>50.0636444808471</v>
       </c>
     </row>
@@ -2080,37 +2372,55 @@
         <v>14.78141276041667</v>
       </c>
       <c r="L10" t="n">
+        <v>14.78141276041667</v>
+      </c>
+      <c r="M10" t="n">
         <v>14.18115234375</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>14.18115234375</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.439335368449671</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>2.439335368449671</v>
+      </c>
+      <c r="Q10" t="n">
         <v>12.6982421875</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
+        <v>12.6982421875</v>
+      </c>
+      <c r="S10" t="n">
         <v>17.46484375</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>17.46484375</v>
+      </c>
+      <c r="U10" t="n">
         <v>44.34423828125</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
+        <v>44.34423828125</v>
+      </c>
+      <c r="W10" t="n">
         <v>812</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;float, float, false&gt;(int, float, float const*, float const*, float const*, float*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(44.344), 'mean_duration_us': np.float64(14.781333333333334), 'median_duration_us': np.float64(14.181), 'std_dev_duration_us': np.float64(1.99187890082594), 'min_duration_us': np.float64(12.698), 'max_duration_us': np.float64(17.465)}]</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(14.78)}]</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="Z10" t="n">
         <v>4.470224916543529</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AA10" t="n">
         <v>54.53386939739063</v>
       </c>
     </row>
@@ -2167,37 +2477,55 @@
         <v>14.00455729166667</v>
       </c>
       <c r="L11" t="n">
+        <v>14.00455729166667</v>
+      </c>
+      <c r="M11" t="n">
         <v>13.056640625</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>13.056640625</v>
+      </c>
+      <c r="O11" t="n">
         <v>3.211196233097079</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
+        <v>3.211196233097079</v>
+      </c>
+      <c r="Q11" t="n">
         <v>11.3740234375</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
+        <v>11.3740234375</v>
+      </c>
+      <c r="S11" t="n">
         <v>17.5830078125</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>17.5830078125</v>
+      </c>
+      <c r="U11" t="n">
         <v>42.013671875</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
+        <v>42.013671875</v>
+      </c>
+      <c r="W11" t="n">
         <v>39</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(14.658999999999999), 'mean_duration_us': np.float64(4.886333333333333), 'median_duration_us': np.float64(4.446), 'std_dev_duration_us': np.float64(0.9517430792440201), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(6.208)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.617), 'mean_duration_us': np.float64(4.539000000000001), 'median_duration_us': np.float64(4.045), 'std_dev_duration_us': np.float64(1.026369329237775), 'min_duration_us': np.float64(3.604), 'max_duration_us': np.float64(5.968)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.738), 'mean_duration_us': np.float64(4.5793333333333335), 'median_duration_us': np.float64(4.566), 'std_dev_duration_us': np.float64(0.6704099906441994), 'min_duration_us': np.float64(3.765), 'max_duration_us': np.float64(5.407)}]</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.89)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(4.54)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}]</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="Z11" t="n">
         <v>4.235286705342297</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AA11" t="n">
         <v>58.76915610273293</v>
       </c>
     </row>
@@ -2254,37 +2582,55 @@
         <v>12.88525390625</v>
       </c>
       <c r="L12" t="n">
+        <v>12.88525390625</v>
+      </c>
+      <c r="M12" t="n">
         <v>12.41796875</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>12.41796875</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.9514369086207531</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>0.9514369086207531</v>
+      </c>
+      <c r="Q12" t="n">
         <v>12.2578125</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
+        <v>12.2578125</v>
+      </c>
+      <c r="S12" t="n">
         <v>13.97998046875</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>13.97998046875</v>
+      </c>
+      <c r="U12" t="n">
         <v>38.65576171875</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
+        <v>38.65576171875</v>
+      </c>
+      <c r="W12" t="n">
         <v>935</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;float, float, false&gt;(int, float, float const*, float const*, float const*, float*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(38.656), 'mean_duration_us': np.float64(12.885333333333334), 'median_duration_us': np.float64(12.418), 'std_dev_duration_us': np.float64(0.7767974138874454), 'min_duration_us': np.float64(12.258), 'max_duration_us': np.float64(13.98)}]</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(12.89)}]</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="Z12" t="n">
         <v>3.896784698547646</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AA12" t="n">
         <v>62.66594080128058</v>
       </c>
     </row>
@@ -2341,37 +2687,55 @@
         <v>11.34928385416667</v>
       </c>
       <c r="L13" t="n">
+        <v>11.34928385416667</v>
+      </c>
+      <c r="M13" t="n">
         <v>11.3759765625</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>11.3759765625</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.0833479550567492</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>0.0833479550567492</v>
+      </c>
+      <c r="Q13" t="n">
         <v>11.255859375</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
+        <v>11.255859375</v>
+      </c>
+      <c r="S13" t="n">
         <v>11.416015625</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
+        <v>11.416015625</v>
+      </c>
+      <c r="U13" t="n">
         <v>34.0478515625</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
+        <v>34.0478515625</v>
+      </c>
+      <c r="W13" t="n">
         <v>60</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_backward_kernel&lt;float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, bool, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(34.048), 'mean_duration_us': np.float64(11.349333333333334), 'median_duration_us': np.float64(11.376), 'std_dev_duration_us': np.float64(0.06798692684790375), 'min_duration_us': np.float64(11.256), 'max_duration_us': np.float64(11.416)}]</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_backward_kernel&lt;float, float, float,...', 'stream': 0, 'mean_duration_us': np.float64(11.35)}]</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="Z13" t="n">
         <v>3.432273510802826</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AA13" t="n">
         <v>66.0982143120834</v>
       </c>
     </row>
@@ -2428,37 +2792,55 @@
         <v>10.96158854166667</v>
       </c>
       <c r="L14" t="n">
+        <v>10.96158854166667</v>
+      </c>
+      <c r="M14" t="n">
         <v>11.4150390625</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>11.4150390625</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.728310461135143</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
+        <v>1.728310461135143</v>
+      </c>
+      <c r="Q14" t="n">
         <v>9.0517578125</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
+        <v>9.0517578125</v>
+      </c>
+      <c r="S14" t="n">
         <v>12.41796875</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
+        <v>12.41796875</v>
+      </c>
+      <c r="U14" t="n">
         <v>32.884765625</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
+        <v>32.884765625</v>
+      </c>
+      <c r="W14" t="n">
         <v>944</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.149), 'mean_duration_us': np.float64(7.049666666666667), 'median_duration_us': np.float64(6.809), 'std_dev_duration_us': np.float64(0.4280197295556465), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(7.651)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.736), 'mean_duration_us': np.float64(3.9120000000000004), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.0972787552243353), 'min_duration_us': np.float64(2.363), 'max_duration_us': np.float64(4.767)}]</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.05)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.91)}]</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="Z14" t="n">
         <v>3.315025905715599</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AA14" t="n">
         <v>69.413240217799</v>
       </c>
     </row>
@@ -2515,37 +2897,55 @@
         <v>10.44091796875</v>
       </c>
       <c r="L15" t="n">
+        <v>10.44091796875</v>
+      </c>
+      <c r="M15" t="n">
         <v>10.61376953125</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>10.61376953125</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.270567767218884</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
+        <v>1.270567767218884</v>
+      </c>
+      <c r="Q15" t="n">
         <v>9.0927734375</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
+        <v>9.0927734375</v>
+      </c>
+      <c r="S15" t="n">
         <v>11.6162109375</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
+        <v>11.6162109375</v>
+      </c>
+      <c r="U15" t="n">
         <v>31.32275390625</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="V15" t="n">
+        <v>31.32275390625</v>
+      </c>
+      <c r="W15" t="n">
         <v>988</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(31.323), 'mean_duration_us': np.float64(10.441), 'median_duration_us': np.float64(10.614), 'std_dev_duration_us': np.float64(1.0372492468061858), 'min_duration_us': np.float64(9.093), 'max_duration_us': np.float64(11.616)}]</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(10.44)}]</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="Z15" t="n">
         <v>3.157563651864197</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AA15" t="n">
         <v>72.57080386966319</v>
       </c>
     </row>
@@ -2602,37 +3002,55 @@
         <v>4.331949869791667</v>
       </c>
       <c r="L16" t="n">
+        <v>4.331949869791667</v>
+      </c>
+      <c r="M16" t="n">
         <v>4.205078125</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>4.205078125</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.094212784726151</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
+        <v>1.094212784726151</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.1630859375</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
+        <v>3.1630859375</v>
+      </c>
+      <c r="S16" t="n">
         <v>6.0078125</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
+        <v>6.0078125</v>
+      </c>
+      <c r="U16" t="n">
         <v>25.99169921875</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="V16" t="n">
+        <v>25.99169921875</v>
+      </c>
+      <c r="W16" t="n">
         <v>103</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;float, at::native::func_wrapper_t&lt;float, at::native::sum_functor&lt;float, float, float&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::func_wrapper_t&lt;float, at::native::sum_functor&lt;float, float, float&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(25.992), 'mean_duration_us': np.float64(4.332), 'median_duration_us': np.float64(4.205), 'std_dev_duration_us': np.float64(0.99894327499947), 'min_duration_us': np.float64(3.163), 'max_duration_us': np.float64(6.008)}]</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(4.33)}]</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="Z16" t="n">
         <v>2.620154184046253</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AA16" t="n">
         <v>75.19095805370945</v>
       </c>
     </row>
@@ -2689,37 +3107,55 @@
         <v>1.885009765625</v>
       </c>
       <c r="L17" t="n">
+        <v>1.885009765625</v>
+      </c>
+      <c r="M17" t="n">
         <v>1.9013671875</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>1.9013671875</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.07718424959046567</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
+        <v>0.07718424959046567</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.76123046875</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
+        <v>1.76123046875</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.9619140625</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>1.9619140625</v>
+      </c>
+      <c r="U17" t="n">
         <v>22.6201171875</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="V17" t="n">
+        <v>22.6201171875</v>
+      </c>
+      <c r="W17" t="n">
         <v>286</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(22.621), 'mean_duration_us': np.float64(1.8850833333333332), 'median_duration_us': np.float64(1.9015), 'std_dev_duration_us': np.float64(0.07396447157626122), 'min_duration_us': np.float64(1.761), 'max_duration_us': np.float64(1.962)}]</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(1.89)}]</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="Z17" t="n">
         <v>2.28027395183496</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AA17" t="n">
         <v>77.47123200554441</v>
       </c>
     </row>
@@ -2776,37 +3212,55 @@
         <v>3.444091796875</v>
       </c>
       <c r="L18" t="n">
+        <v>3.444091796875</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.50390625</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>3.50390625</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.8804555436695012</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
+        <v>0.8804555436695012</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.08203125</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
+        <v>2.08203125</v>
+      </c>
+      <c r="S18" t="n">
         <v>4.52587890625</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>4.52587890625</v>
+      </c>
+      <c r="U18" t="n">
         <v>20.66455078125</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="V18" t="n">
+        <v>20.66455078125</v>
+      </c>
+      <c r="W18" t="n">
         <v>844</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(20.665000000000003), 'mean_duration_us': np.float64(3.4441666666666673), 'median_duration_us': np.float64(3.504), 'std_dev_duration_us': np.float64(0.8038002273920775), 'min_duration_us': np.float64(2.082), 'max_duration_us': np.float64(4.526)}]</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.44)}]</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="Z18" t="n">
         <v>2.083138494918778</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
         <v>79.55437050046319</v>
       </c>
     </row>
@@ -2863,37 +3317,55 @@
         <v>3.303955078125</v>
       </c>
       <c r="L19" t="n">
+        <v>3.303955078125</v>
+      </c>
+      <c r="M19" t="n">
         <v>3.58447265625</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>3.58447265625</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.113728012655698</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>1.113728012655698</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1.8818359375</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
+        <v>1.8818359375</v>
+      </c>
+      <c r="S19" t="n">
         <v>4.60498046875</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
+        <v>4.60498046875</v>
+      </c>
+      <c r="U19" t="n">
         <v>19.82373046875</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="V19" t="n">
+        <v>19.82373046875</v>
+      </c>
+      <c r="W19" t="n">
         <v>799</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;long&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(19.823999999999998), 'mean_duration_us': np.float64(3.304), 'median_duration_us': np.float64(3.5845000000000002), 'std_dev_duration_us': np.float64(1.0166421854975984), 'min_duration_us': np.float64(1.882), 'max_duration_us': np.float64(4.605)}]</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(3.3)}]</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="Z19" t="n">
         <v>1.998377631795267</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
         <v>81.55274813225846</v>
       </c>
     </row>
@@ -2950,37 +3422,55 @@
         <v>6.582356770833333</v>
       </c>
       <c r="L20" t="n">
+        <v>6.582356770833333</v>
+      </c>
+      <c r="M20" t="n">
         <v>6.3291015625</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>6.3291015625</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.849598477465432</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
+        <v>0.849598477465432</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5.88818359375</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
+        <v>5.88818359375</v>
+      </c>
+      <c r="S20" t="n">
         <v>7.52978515625</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>7.52978515625</v>
+      </c>
+      <c r="U20" t="n">
         <v>19.7470703125</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="V20" t="n">
+        <v>19.7470703125</v>
+      </c>
+      <c r="W20" t="n">
         <v>23</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_backward_kernel&lt;float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::DefaultPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::DefaultPtrTraits, int&gt;, bool, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(19.747), 'mean_duration_us': np.float64(6.582333333333334), 'median_duration_us': np.float64(6.329), 'std_dev_duration_us': np.float64(0.6938656610292484), 'min_duration_us': np.float64(5.888), 'max_duration_us': np.float64(7.53)}]</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::batch_norm_backward_kernel&lt;float, float, float,...', 'stream': 0, 'mean_duration_us': np.float64(6.58)}]</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="Z20" t="n">
         <v>1.990649724994807</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
         <v>83.54339785725327</v>
       </c>
     </row>
@@ -3037,37 +3527,55 @@
         <v>5.861002604166667</v>
       </c>
       <c r="L21" t="n">
+        <v>5.861002604166667</v>
+      </c>
+      <c r="M21" t="n">
         <v>5.48681640625</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>5.48681640625</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.8640909439748991</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
+        <v>0.8640909439748991</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5.2470703125</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
+        <v>5.2470703125</v>
+      </c>
+      <c r="S21" t="n">
         <v>6.84912109375</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>6.84912109375</v>
+      </c>
+      <c r="U21" t="n">
         <v>17.5830078125</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="V21" t="n">
+        <v>17.5830078125</v>
+      </c>
+      <c r="W21" t="n">
         <v>13</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, true&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(17.583), 'mean_duration_us': np.float64(5.861), 'median_duration_us': np.float64(5.487), 'std_dev_duration_us': np.float64(0.705458716013914), 'min_duration_us': np.float64(5.247), 'max_duration_us': np.float64(6.849)}]</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.86)}]</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="Z21" t="n">
         <v>1.772496330474828</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AA21" t="n">
         <v>85.31589418772809</v>
       </c>
     </row>
@@ -3124,37 +3632,55 @@
         <v>4.114990234375</v>
       </c>
       <c r="L22" t="n">
+        <v>4.114990234375</v>
+      </c>
+      <c r="M22" t="n">
         <v>4.10498046875</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>4.10498046875</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.2909463889692953</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
+        <v>0.2909463889692953</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.84521484375</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
+        <v>3.84521484375</v>
+      </c>
+      <c r="S22" t="n">
         <v>4.40478515625</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
+        <v>4.40478515625</v>
+      </c>
+      <c r="U22" t="n">
         <v>16.4599609375</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="V22" t="n">
+        <v>16.4599609375</v>
+      </c>
+      <c r="W22" t="n">
         <v>333</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 4, 'total_duration_us': np.float64(16.459999999999997), 'mean_duration_us': np.float64(4.114999999999999), 'median_duration_us': np.float64(4.105), 'std_dev_duration_us': np.float64(0.2519920633670832), 'min_duration_us': np.float64(3.845), 'max_duration_us': np.float64(4.405)}]</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.11)}]</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="Z22" t="n">
         <v>1.659284956964911</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AA22" t="n">
         <v>86.975179144693</v>
       </c>
     </row>
@@ -3211,37 +3737,55 @@
         <v>5.099934895833333</v>
       </c>
       <c r="L23" t="n">
+        <v>5.099934895833333</v>
+      </c>
+      <c r="M23" t="n">
         <v>5.0068359375</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>5.0068359375</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.4674548588682645</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
+        <v>0.4674548588682645</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.68603515625</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
+        <v>4.68603515625</v>
+      </c>
+      <c r="S23" t="n">
         <v>5.60693359375</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
+        <v>5.60693359375</v>
+      </c>
+      <c r="U23" t="n">
         <v>15.2998046875</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="V23" t="n">
+        <v>15.2998046875</v>
+      </c>
+      <c r="W23" t="n">
         <v>167</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormBwdSpatial', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(15.3), 'mean_duration_us': np.float64(5.1000000000000005), 'median_duration_us': np.float64(5.007), 'std_dev_duration_us': np.float64(0.38170407385827065), 'min_duration_us': np.float64(4.686), 'max_duration_us': np.float64(5.607)}]</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormBwdSpatial', 'stream': 0, 'mean_duration_us': np.float64(5.1)}]</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="Z23" t="n">
         <v>1.542332685895536</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AA23" t="n">
         <v>88.51751183058853</v>
       </c>
     </row>
@@ -3298,37 +3842,55 @@
         <v>4.61962890625</v>
       </c>
       <c r="L24" t="n">
+        <v>4.61962890625</v>
+      </c>
+      <c r="M24" t="n">
         <v>4.205078125</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>4.205078125</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7875207625785555</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
+        <v>0.7875207625785555</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4.1259765625</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
+        <v>4.1259765625</v>
+      </c>
+      <c r="S24" t="n">
         <v>5.52783203125</v>
       </c>
-      <c r="P24" t="n">
+      <c r="T24" t="n">
+        <v>5.52783203125</v>
+      </c>
+      <c r="U24" t="n">
         <v>13.85888671875</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="V24" t="n">
+        <v>13.85888671875</v>
+      </c>
+      <c r="W24" t="n">
         <v>912</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;float, float, true&gt;(int, float, float const*, float const*, float const*, float*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.859000000000002), 'mean_duration_us': np.float64(4.619666666666667), 'median_duration_us': np.float64(4.205), 'std_dev_duration_us': np.float64(0.6430978843760011), 'min_duration_us': np.float64(4.126), 'max_duration_us': np.float64(5.528)}]</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(4.62)}]</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="Z24" t="n">
         <v>1.397077571448682</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AA24" t="n">
         <v>89.91458940203721</v>
       </c>
     </row>
@@ -3385,37 +3947,55 @@
         <v>4.47265625</v>
       </c>
       <c r="L25" t="n">
+        <v>4.47265625</v>
+      </c>
+      <c r="M25" t="n">
         <v>4.2861328125</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>4.2861328125</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.5838267646323473</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
+        <v>0.5838267646323473</v>
+      </c>
+      <c r="Q25" t="n">
         <v>4.0048828125</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
+        <v>4.0048828125</v>
+      </c>
+      <c r="S25" t="n">
         <v>5.126953125</v>
       </c>
-      <c r="P25" t="n">
+      <c r="T25" t="n">
+        <v>5.126953125</v>
+      </c>
+      <c r="U25" t="n">
         <v>13.41796875</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="V25" t="n">
+        <v>13.41796875</v>
+      </c>
+      <c r="W25" t="n">
         <v>88</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormBwdSpatial', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.418), 'mean_duration_us': np.float64(4.472666666666666), 'median_duration_us': np.float64(4.286), 'std_dev_duration_us': np.float64(0.4766930062652715), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(5.127)}]</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormBwdSpatial', 'stream': 0, 'mean_duration_us': np.float64(4.47)}]</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="Z25" t="n">
         <v>1.352629801761963</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AA25" t="n">
         <v>91.26721920379917</v>
       </c>
     </row>
@@ -3472,37 +4052,55 @@
         <v>4.459147135416667</v>
       </c>
       <c r="L26" t="n">
+        <v>4.459147135416667</v>
+      </c>
+      <c r="M26" t="n">
         <v>4.24609375</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
+        <v>4.24609375</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.3698653385043163</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
+        <v>0.3698653385043163</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4.2451171875</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
+        <v>4.2451171875</v>
+      </c>
+      <c r="S26" t="n">
         <v>4.88623046875</v>
       </c>
-      <c r="P26" t="n">
+      <c r="T26" t="n">
+        <v>4.88623046875</v>
+      </c>
+      <c r="U26" t="n">
         <v>13.37744140625</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="V26" t="n">
+        <v>13.37744140625</v>
+      </c>
+      <c r="W26" t="n">
         <v>975</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;float, float, true&gt;(int, float, float const*, float const*, float const*, float*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.377000000000002), 'mean_duration_us': np.float64(4.4590000000000005), 'median_duration_us': np.float64(4.246), 'std_dev_duration_us': np.float64(0.30193487156449256), 'min_duration_us': np.float64(4.245), 'max_duration_us': np.float64(4.886)}]</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_ke...', 'stream': 0, 'mean_duration_us': np.float64(4.46)}]</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="Z26" t="n">
         <v>1.348544347848344</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AA26" t="n">
         <v>92.61576355164752</v>
       </c>
     </row>
@@ -3559,37 +4157,55 @@
         <v>4.458821614583333</v>
       </c>
       <c r="L27" t="n">
+        <v>4.458821614583333</v>
+      </c>
+      <c r="M27" t="n">
         <v>4.365234375</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
+        <v>4.365234375</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.3500872140033832</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
+        <v>0.3500872140033832</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4.1650390625</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
+        <v>4.1650390625</v>
+      </c>
+      <c r="S27" t="n">
         <v>4.84619140625</v>
       </c>
-      <c r="P27" t="n">
+      <c r="T27" t="n">
+        <v>4.84619140625</v>
+      </c>
+      <c r="U27" t="n">
         <v>13.37646484375</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="V27" t="n">
+        <v>13.37646484375</v>
+      </c>
+      <c r="W27" t="n">
         <v>982</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::distribution_elementwise_grid_stride_kernel&lt;float, 4, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2}, at::native::(anonymous namespace)::distribution_nullary_kernel&lt;float, float, HIP_vector_type&lt;float, 4u&gt;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2}, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2} const&amp;, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(int, float)#1}&gt;(long, at::PhiloxCudaState, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2}, at::native::(anonymous namespace)::distribution_nullary_kernel&lt;float, float, HIP_vector_type&lt;float, 4u&gt;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2}, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_and_transform&lt;float, float, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::CUDAGeneratorImpl*, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(hiprandStatePhilox4_32_10*)#2} const&amp;, at::native::templates::cuda::normal_kernel&lt;at::CUDAGeneratorImpl*&gt;(at::TensorBase const&amp;, double, double, at::CUDAGeneratorImpl*)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1})::{lambda(int, float)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.376000000000001), 'mean_duration_us': np.float64(4.458666666666667), 'median_duration_us': np.float64(4.365), 'std_dev_duration_us': np.float64(0.28579751962223576), 'min_duration_us': np.float64(4.165), 'max_duration_us': np.float64(4.846)}]</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::distribution_elementwise...', 'stream': 0, 'mean_duration_us': np.float64(4.46)}]</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="Z27" t="n">
         <v>1.348445903175727</v>
       </c>
-      <c r="U27" t="n">
+      <c r="AA27" t="n">
         <v>93.96420945482325</v>
       </c>
     </row>
@@ -3646,37 +4262,55 @@
         <v>4.446451822916667</v>
       </c>
       <c r="L28" t="n">
+        <v>4.446451822916667</v>
+      </c>
+      <c r="M28" t="n">
         <v>4.2861328125</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>4.2861328125</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.9320300852322503</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
+        <v>0.9320300852322503</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.60498046875</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
+        <v>3.60498046875</v>
+      </c>
+      <c r="S28" t="n">
         <v>5.4482421875</v>
       </c>
-      <c r="P28" t="n">
+      <c r="T28" t="n">
+        <v>5.4482421875</v>
+      </c>
+      <c r="U28" t="n">
         <v>13.33935546875</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="V28" t="n">
+        <v>13.33935546875</v>
+      </c>
+      <c r="W28" t="n">
         <v>9</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.339), 'mean_duration_us': np.float64(4.4463333333333335), 'median_duration_us': np.float64(4.286), 'std_dev_duration_us': np.float64(0.7608952329693989), 'min_duration_us': np.float64(3.605), 'max_duration_us': np.float64(5.448)}]</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.45)}]</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="Z28" t="n">
         <v>1.344705005616269</v>
       </c>
-      <c r="U28" t="n">
+      <c r="AA28" t="n">
         <v>95.30891446043951</v>
       </c>
     </row>
@@ -3733,37 +4367,55 @@
         <v>4.352213541666667</v>
       </c>
       <c r="L29" t="n">
+        <v>4.352213541666667</v>
+      </c>
+      <c r="M29" t="n">
         <v>4.1650390625</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
+        <v>4.1650390625</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.5456305012929936</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
+        <v>0.5456305012929936</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.9248046875</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
+        <v>3.9248046875</v>
+      </c>
+      <c r="S29" t="n">
         <v>4.966796875</v>
       </c>
-      <c r="P29" t="n">
+      <c r="T29" t="n">
+        <v>4.966796875</v>
+      </c>
+      <c r="U29" t="n">
         <v>13.056640625</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="V29" t="n">
+        <v>13.056640625</v>
+      </c>
+      <c r="W29" t="n">
         <v>901</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.056999999999999), 'mean_duration_us': np.float64(4.352333333333333), 'median_duration_us': np.float64(4.165), 'std_dev_duration_us': np.float64(0.4455418673430763), 'min_duration_us': np.float64(3.925), 'max_duration_us': np.float64(4.967)}]</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>[{'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'mean_duration_us': np.float64(4.35)}]</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="Z29" t="n">
         <v>1.316205272893555</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AA29" t="n">
         <v>96.62511973333307</v>
       </c>
     </row>
@@ -3820,37 +4472,55 @@
         <v>3.77783203125</v>
       </c>
       <c r="L30" t="n">
+        <v>14.21875</v>
+      </c>
+      <c r="M30" t="n">
         <v>3.48388671875</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>14.09765625</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.6160871136487144</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
+        <v>1.825768215017019</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.36376953125</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
+        <v>12.45654296875</v>
+      </c>
+      <c r="S30" t="n">
         <v>4.48583984375</v>
       </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
+        <v>16.10205078125</v>
+      </c>
+      <c r="U30" t="n">
         <v>11.33349609375</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="V30" t="n">
+        <v>42.65625</v>
+      </c>
+      <c r="W30" t="n">
         <v>984</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.334), 'mean_duration_us': np.float64(3.778), 'median_duration_us': np.float64(3.484), 'std_dev_duration_us': np.float64(0.503022862303494), 'min_duration_us': np.float64(3.364), 'max_duration_us': np.float64(4.486)}]</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ms...', 'stream': 0, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="Z30" t="n">
         <v>1.142499648060296</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AA30" t="n">
         <v>97.76761938139336</v>
       </c>
     </row>
@@ -3907,37 +4577,55 @@
         <v>3.150390625</v>
       </c>
       <c r="L31" t="n">
+        <v>3.150390625</v>
+      </c>
+      <c r="M31" t="n">
         <v>2.9228515625</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>2.9228515625</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.5757850512271701</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
+        <v>0.5757850512271701</v>
+      </c>
+      <c r="Q31" t="n">
         <v>2.72314453125</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
+        <v>2.72314453125</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.80517578125</v>
       </c>
-      <c r="P31" t="n">
+      <c r="T31" t="n">
+        <v>3.80517578125</v>
+      </c>
+      <c r="U31" t="n">
         <v>9.451171875</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="V31" t="n">
+        <v>9.451171875</v>
+      </c>
+      <c r="W31" t="n">
         <v>8</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.451), 'mean_duration_us': np.float64(3.1503333333333337), 'median_duration_us': np.float64(2.923), 'std_dev_duration_us': np.float64(0.4700647709506521), 'min_duration_us': np.float64(2.723), 'max_duration_us': np.float64(3.805)}]</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(3.15)}]</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="Z31" t="n">
         <v>0.9527475415904131</v>
       </c>
-      <c r="U31" t="n">
+      <c r="AA31" t="n">
         <v>98.72036692298377</v>
       </c>
     </row>
@@ -3994,37 +4682,55 @@
         <v>2.722981770833333</v>
       </c>
       <c r="L32" t="n">
+        <v>2.722981770833333</v>
+      </c>
+      <c r="M32" t="n">
         <v>3.04296875</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>3.04296875</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.772600022376397</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
+        <v>0.772600022376397</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1.841796875</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
+        <v>1.841796875</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.2841796875</v>
       </c>
-      <c r="P32" t="n">
+      <c r="T32" t="n">
+        <v>3.2841796875</v>
+      </c>
+      <c r="U32" t="n">
         <v>8.1689453125</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="V32" t="n">
+        <v>8.1689453125</v>
+      </c>
+      <c r="W32" t="n">
         <v>993</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;float&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(8.169), 'mean_duration_us': np.float64(2.7230000000000003), 'median_duration_us': np.float64(3.043), 'std_dev_duration_us': np.float64(0.6306826988800839), 'min_duration_us': np.float64(1.842), 'max_duration_us': np.float64(3.284)}]</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(2.72)}]</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="Z32" t="n">
         <v>0.8234896864438732</v>
       </c>
-      <c r="U32" t="n">
+      <c r="AA32" t="n">
         <v>99.54385660942765</v>
       </c>
     </row>
@@ -4084,34 +4790,52 @@
         <v>2.262451171875</v>
       </c>
       <c r="M33" t="n">
+        <v>2.262451171875</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.262451171875</v>
+      </c>
+      <c r="O33" t="n">
         <v>0.2551523004379193</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
+        <v>0.2551523004379193</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.08203125</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
+        <v>2.08203125</v>
+      </c>
+      <c r="S33" t="n">
         <v>2.44287109375</v>
       </c>
-      <c r="P33" t="n">
+      <c r="T33" t="n">
+        <v>2.44287109375</v>
+      </c>
+      <c r="U33" t="n">
         <v>4.52490234375</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="V33" t="n">
+        <v>4.52490234375</v>
+      </c>
+      <c r="W33" t="n">
         <v>258</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;float&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 2, 'total_duration_us': np.float64(4.525), 'mean_duration_us': np.float64(2.2625), 'median_duration_us': np.float64(2.2625), 'std_dev_duration_us': np.float64(0.18050000000000008), 'min_duration_us': np.float64(2.082), 'max_duration_us': np.float64(2.443)}]</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(2.26)}]</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="Z33" t="n">
         <v>0.4561433905723475</v>
       </c>
-      <c r="U33" t="n">
+      <c r="AA33" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4480,12 +5204,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, false&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(84.883), 'mean_duration_us': np.float64(28.29433333333333), 'median_duration_us': np.float64(28.201), 'std_dev_duration_us': np.float64(0.4143543840187468), 'min_duration_us': np.float64(27.84), 'max_duration_us': np.float64(28.842)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleCUDAKernel&lt;float, float, false&gt;(long, long, float const*, float const*, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.936999999999998), 'mean_duration_us': np.float64(4.312333333333332), 'median_duration_us': np.float64(4.406), 'std_dev_duration_us': np.float64(0.16157626338323602), 'min_duration_us': np.float64(4.085), 'max_duration_us': np.float64(4.446)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleCUDAKernel&lt;float, float, false&gt;(long, long, float const*, float const*, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.936999999999998), 'mean_duration_us': np.float64(4.312333333333332), 'median_duration_us': np.float64(4.406), 'std_dev_duration_us': np.float64(0.16157626338323602), 'min_duration_us': np.float64(4.085), 'max_duration_us': np.float64(4.446)}, {'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, false&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(84.883), 'mean_duration_us': np.float64(28.29433333333333), 'median_duration_us': np.float64(28.201), 'std_dev_duration_us': np.float64(0.4143543840187468), 'min_duration_us': np.float64(27.84), 'max_duration_us': np.float64(28.842)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(28.29)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleC...', 'stream': 0, 'mean_duration_us': np.float64(4.31)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardSimpleC...', 'stream': 0, 'mean_duration_us': np.float64(4.31)}, {'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(28.29)}]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -4794,12 +5518,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(37.091), 'mean_duration_us': np.float64(12.363666666666667), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(12.076039232942046), 'min_duration_us': np.float64(3.685), 'max_duration_us': np.float64(29.441)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(15.74), 'mean_duration_us': np.float64(5.246666666666667), 'median_duration_us': np.float64(4.926), 'std_dev_duration_us': np.float64(0.6308519812303217), 'min_duration_us': np.float64(4.686), 'max_duration_us': np.float64(6.128)}, {'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.535), 'mean_duration_us': np.float64(4.178333333333334), 'median_duration_us': np.float64(4.125), 'std_dev_duration_us': np.float64(0.07542472332656514), 'min_duration_us': np.float64(4.125), 'max_duration_us': np.float64(4.285)}]</t>
+          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.535), 'mean_duration_us': np.float64(4.178333333333334), 'median_duration_us': np.float64(4.125), 'std_dev_duration_us': np.float64(0.07542472332656514), 'min_duration_us': np.float64(4.125), 'max_duration_us': np.float64(4.285)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(15.74), 'mean_duration_us': np.float64(5.246666666666667), 'median_duration_us': np.float64(4.926), 'std_dev_duration_us': np.float64(0.6308519812303217), 'min_duration_us': np.float64(4.686), 'max_duration_us': np.float64(6.128)}, {'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(37.091), 'mean_duration_us': np.float64(12.363666666666667), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(12.076039232942046), 'min_duration_us': np.float64(3.685), 'max_duration_us': np.float64(29.441)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(12.36)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(5.25)}, {'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'mean_duration_us': np.float64(4.18)}]</t>
+          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatialNorm', 'stream': 0, 'mean_duration_us': np.float64(4.18)}, {'name': 'MIOpenBatchNormFwdTrainSpatialFinalMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(5.25)}, {'name': 'MIOpenBatchNormFwdTrainSpatialMeanVariance', 'stream': 0, 'mean_duration_us': np.float64(12.36)}]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -4951,12 +5675,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.216000000000001), 'mean_duration_us': np.float64(4.405333333333334), 'median_duration_us': np.float64(4.405), 'std_dev_duration_us': np.float64(0.1963675691712412), 'min_duration_us': np.float64(4.165), 'max_duration_us': np.float64(4.646)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(6.327), 'mean_duration_us': np.float64(2.109), 'median_duration_us': np.float64(2.122), 'std_dev_duration_us': np.float64(0.24552936009094037), 'min_duration_us': np.float64(1.802), 'max_duration_us': np.float64(2.403)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.370999999999999), 'mean_duration_us': np.float64(3.1236666666666664), 'median_duration_us': np.float64(2.723), 'std_dev_duration_us': np.float64(0.624051992135983), 'min_duration_us': np.float64(2.643), 'max_duration_us': np.float64(4.005)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.942), 'mean_duration_us': np.float64(5.647333333333333), 'median_duration_us': np.float64(4.726), 'std_dev_duration_us': np.float64(1.4759235150312575), 'min_duration_us': np.float64(4.486), 'max_duration_us': np.float64(7.73)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKernel1&lt;float&gt;(long, long, long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.415), 'mean_duration_us': np.float64(4.138333333333333), 'median_duration_us': np.float64(4.085), 'std_dev_duration_us': np.float64(0.1359738536958077), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(4.325)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKernel1&lt;float&gt;(long, long, long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.415), 'mean_duration_us': np.float64(4.138333333333333), 'median_duration_us': np.float64(4.085), 'std_dev_duration_us': np.float64(0.1359738536958077), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(4.325)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.942), 'mean_duration_us': np.float64(5.647333333333333), 'median_duration_us': np.float64(4.726), 'std_dev_duration_us': np.float64(1.4759235150312575), 'min_duration_us': np.float64(4.486), 'max_duration_us': np.float64(7.73)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.370999999999999), 'mean_duration_us': np.float64(3.1236666666666664), 'median_duration_us': np.float64(2.723), 'std_dev_duration_us': np.float64(0.624051992135983), 'min_duration_us': np.float64(2.643), 'max_duration_us': np.float64(4.005)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(6.327), 'mean_duration_us': np.float64(2.109), 'median_duration_us': np.float64(2.122), 'std_dev_duration_us': np.float64(0.24552936009094037), 'min_duration_us': np.float64(1.802), 'max_duration_us': np.float64(2.403)}, {'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.216000000000001), 'mean_duration_us': np.float64(4.405333333333334), 'median_duration_us': np.float64(4.405), 'std_dev_duration_us': np.float64(0.1963675691712412), 'min_duration_us': np.float64(4.165), 'max_duration_us': np.float64(4.646)}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.41)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(2.11)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(3.12)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.65)}, {'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKer...', 'stream': 0, 'mean_duration_us': np.float64(4.14)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::GammaBetaBackwardCUDAKer...', 'stream': 0, 'mean_duration_us': np.float64(4.14)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.65)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(3.12)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(2.11)}, {'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.41)}]</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -5108,12 +5832,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(32.966), 'mean_duration_us': np.float64(10.988666666666667), 'median_duration_us': np.float64(11.376), 'std_dev_duration_us': np.float64(0.5762877367735286), 'min_duration_us': np.float64(10.174), 'max_duration_us': np.float64(11.416)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_kernel_for_multi_outputs&lt;3, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.530000000000001), 'mean_duration_us': np.float64(3.176666666666667), 'median_duration_us': np.float64(3.644), 'std_dev_duration_us': np.float64(0.8672271264720037), 'min_duration_us': np.float64(1.961), 'max_duration_us': np.float64(3.925)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(10.693999999999999), 'mean_duration_us': np.float64(3.564666666666666), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.7857575255057304), 'min_duration_us': np.float64(2.483), 'max_duration_us': np.float64(4.326)}]</t>
+          <t>[{'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(10.693999999999999), 'mean_duration_us': np.float64(3.564666666666666), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.7857575255057304), 'min_duration_us': np.float64(2.483), 'max_duration_us': np.float64(4.326)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_kernel_for_multi_outputs&lt;3, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_update_stats_and_invert(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, double, double, long)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float, float, float)#1}, std::array&lt;char*, 7ul&gt;, TrivialOffsetCalculator&lt;4, unsigned int&gt;, TrivialOffsetCalculator&lt;3, unsigned int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.530000000000001), 'mean_duration_us': np.float64(3.176666666666667), 'median_duration_us': np.float64(3.644), 'std_dev_duration_us': np.float64(0.8672271264720037), 'min_duration_us': np.float64(1.961), 'max_duration_us': np.float64(3.925)}, {'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(32.966), 'mean_duration_us': np.float64(10.988666666666667), 'median_duration_us': np.float64(11.376), 'std_dev_duration_us': np.float64(0.5762877367735286), 'min_duration_us': np.float64(10.174), 'max_duration_us': np.float64(11.416)}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(10.99)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_ker...', 'stream': 0, 'mean_duration_us': np.float64(3.18)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.56)}]</t>
+          <t>[{'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.56)}, {'name': 'void at::native::(anonymous namespace)::unrolled_elementwise_ker...', 'stream': 0, 'mean_duration_us': np.float64(3.18)}, {'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(10.99)}]</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -5265,12 +5989,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.587), 'mean_duration_us': np.float64(6.862333333333333), 'median_duration_us': np.float64(6.568), 'std_dev_duration_us': np.float64(0.8121807406948011), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(7.971)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.865000000000002), 'mean_duration_us': np.float64(6.288333333333334), 'median_duration_us': np.float64(6.369), 'std_dev_duration_us': np.float64(0.17297462883967188), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(6.448)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.895), 'mean_duration_us': np.float64(3.965), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(0.06531972647421815), 'min_duration_us': np.float64(3.885), 'max_duration_us': np.float64(4.045)}]</t>
+          <t>[{'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float, float, true, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, std::conditional&lt;true, float, float&gt;::type, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, std::conditional&lt;true, float, float&gt;::type, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float const, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, float)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.895), 'mean_duration_us': np.float64(3.965), 'median_duration_us': np.float64(3.965), 'std_dev_duration_us': np.float64(0.06531972647421815), 'min_duration_us': np.float64(3.885), 'max_duration_us': np.float64(4.045)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::batch_norm_calc_invstd(at::Tensor const&amp;, at::Tensor const&amp;, double)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.865000000000002), 'mean_duration_us': np.float64(6.288333333333334), 'median_duration_us': np.float64(6.369), 'std_dev_duration_us': np.float64(0.17297462883967188), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(6.448)}, {'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native::Var, float, float, float, int&gt;(torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float const, 2ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;3ul, int&gt;, float const, 3ul, torch::headeronly::RestrictPtrTraits, int&gt;, float, float, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;, torch::headeronly::detail::GenericPackedTensorAccessor&lt;torch::headeronly::detail::TensorAccessor&lt;c10::ArrayRef&lt;long&gt;, float, 0ul, torch::headeronly::RestrictPtrTraits, int&gt;, at::detail::IndexBoundsCheck&lt;1ul, int&gt;, float, 1ul, torch::headeronly::RestrictPtrTraits, int&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.587), 'mean_duration_us': np.float64(6.862333333333333), 'median_duration_us': np.float64(6.568), 'std_dev_duration_us': np.float64(0.8121807406948011), 'min_duration_us': np.float64(6.048), 'max_duration_us': np.float64(7.971)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(6.86)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(6.29)}, {'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.96)}]</t>
+          <t>[{'name': 'void at::native::batch_norm_transform_input_kernel&lt;float, float,...', 'stream': 0, 'mean_duration_us': np.float64(3.96)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(6.29)}, {'name': 'void at::native::batch_norm_collect_statistics_kernel&lt;at::native...', 'stream': 0, 'mean_duration_us': np.float64(6.86)}]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -5422,12 +6146,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, true&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.782999999999998), 'mean_duration_us': np.float64(5.594333333333332), 'median_duration_us': np.float64(5.528), 'std_dev_duration_us': np.float64(0.2178077643754286), 'min_duration_us': np.float64(5.367), 'max_duration_us': np.float64(5.888)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, long, long, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.707), 'mean_duration_us': np.float64(6.902333333333334), 'median_duration_us': np.float64(6.889), 'std_dev_duration_us': np.float64(0.5071320231348923), 'min_duration_us': np.float64(6.288), 'max_duration_us': np.float64(7.53)}, {'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, int, long, long, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.695), 'mean_duration_us': np.float64(3.8983333333333334), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.04988876515698577), 'min_duration_us': np.float64(3.845), 'max_duration_us': np.float64(3.965)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, int, long, long, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.695), 'mean_duration_us': np.float64(3.8983333333333334), 'median_duration_us': np.float64(3.885), 'std_dev_duration_us': np.float64(0.04988876515698577), 'min_duration_us': np.float64(3.845), 'max_duration_us': np.float64(3.965)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBeta&lt;float, float, true&gt;(float const*, float const*, long, long, float const*, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(20.707), 'mean_duration_us': np.float64(6.902333333333334), 'median_duration_us': np.float64(6.889), 'std_dev_duration_us': np.float64(0.5071320231348923), 'min_duration_us': np.float64(6.288), 'max_duration_us': np.float64(7.53)}, {'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_kernel&lt;float, float, true&gt;(float const*, float const*, float const*, float const*, float const*, float*, int)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(16.782999999999998), 'mean_duration_us': np.float64(5.594333333333332), 'median_duration_us': np.float64(5.528), 'std_dev_duration_us': np.float64(0.2178077643754286), 'min_duration_us': np.float64(5.367), 'max_duration_us': np.float64(5.888)}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.59)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBe...', 'stream': 0, 'mean_duration_us': np.float64(6.9)}, {'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;f...', 'stream': 0, 'mean_duration_us': np.float64(3.9)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cuComputeGradGammaBeta&lt;f...', 'stream': 0, 'mean_duration_us': np.float64(3.9)}, {'name': 'void at::native::(anonymous namespace)::cuComputePartGradGammaBe...', 'stream': 0, 'mean_duration_us': np.float64(6.9)}, {'name': 'void at::native::(anonymous namespace)::layer_norm_grad_input_ke...', 'stream': 0, 'mean_duration_us': np.float64(5.59)}]</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -5579,12 +6303,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.869999999999997), 'mean_duration_us': np.float64(7.289999999999999), 'median_duration_us': np.float64(7.17), 'std_dev_duration_us': np.float64(0.5463338417732021), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(8.011)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.296), 'mean_duration_us': np.float64(4.0986666666666665), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.4510511898467109), 'min_duration_us': np.float64(2.123), 'max_duration_us': np.float64(5.567)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.657), 'mean_duration_us': np.float64(4.552333333333333), 'median_duration_us': np.float64(4.285), 'std_dev_duration_us': np.float64(0.7437568300339985), 'min_duration_us': np.float64(3.805), 'max_duration_us': np.float64(5.567)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.657), 'mean_duration_us': np.float64(4.552333333333333), 'median_duration_us': np.float64(4.285), 'std_dev_duration_us': np.float64(0.7437568300339985), 'min_duration_us': np.float64(3.805), 'max_duration_us': np.float64(5.567)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(12.296), 'mean_duration_us': np.float64(4.0986666666666665), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.4510511898467109), 'min_duration_us': np.float64(2.123), 'max_duration_us': np.float64(5.567)}, {'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.869999999999997), 'mean_duration_us': np.float64(7.289999999999999), 'median_duration_us': np.float64(7.17), 'std_dev_duration_us': np.float64(0.5463338417732021), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(8.011)}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.29)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKe...', 'stream': 0, 'mean_duration_us': np.float64(4.1)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.55)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.55)}, {'name': 'void at::native::(anonymous namespace)::ComputeFusedParamsCUDAKe...', 'stream': 0, 'mean_duration_us': np.float64(4.1)}, {'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.29)}]</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -5863,12 +6587,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.334), 'mean_duration_us': np.float64(3.778), 'median_duration_us': np.float64(3.484), 'std_dev_duration_us': np.float64(0.503022862303494), 'min_duration_us': np.float64(3.364), 'max_duration_us': np.float64(4.486)}, {'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(31.323), 'mean_duration_us': np.float64(10.441), 'median_duration_us': np.float64(10.614), 'std_dev_duration_us': np.float64(1.0372492468061858), 'min_duration_us': np.float64(9.093), 'max_duration_us': np.float64(11.616)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(31.323), 'mean_duration_us': np.float64(10.441), 'median_duration_us': np.float64(10.614), 'std_dev_duration_us': np.float64(1.0372492468061858), 'min_duration_us': np.float64(9.093), 'max_duration_us': np.float64(11.616)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#2}::operator()() const::{lambda(float, float)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.334), 'mean_duration_us': np.float64(3.778), 'median_duration_us': np.float64(3.484), 'std_dev_duration_us': np.float64(0.503022862303494), 'min_duration_us': np.float64(3.364), 'max_duration_us': np.float64(4.486)}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ms...', 'stream': 0, 'mean_duration_us': np.float64(3.78)}, {'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(10.44)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(10.44)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::ms...', 'stream': 0, 'mean_duration_us': np.float64(3.78)}]</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr"/>
@@ -6016,12 +6740,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(14.658999999999999), 'mean_duration_us': np.float64(4.886333333333333), 'median_duration_us': np.float64(4.446), 'std_dev_duration_us': np.float64(0.9517430792440201), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(6.208)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.617), 'mean_duration_us': np.float64(4.539000000000001), 'median_duration_us': np.float64(4.045), 'std_dev_duration_us': np.float64(1.026369329237775), 'min_duration_us': np.float64(3.604), 'max_duration_us': np.float64(5.968)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.738), 'mean_duration_us': np.float64(4.5793333333333335), 'median_duration_us': np.float64(4.566), 'std_dev_duration_us': np.float64(0.6704099906441994), 'min_duration_us': np.float64(3.765), 'max_duration_us': np.float64(5.407)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormBackwardKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float, float, float)#2} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.738), 'mean_duration_us': np.float64(4.5793333333333335), 'median_duration_us': np.float64(4.566), 'std_dev_duration_us': np.float64(0.6704099906441994), 'min_duration_us': np.float64(3.765), 'max_duration_us': np.float64(5.407)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedParamsCUDAKernel&lt;float&gt;(long, long, long, float const*, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.617), 'mean_duration_us': np.float64(4.539000000000001), 'median_duration_us': np.float64(4.045), 'std_dev_duration_us': np.float64(1.026369329237775), 'min_duration_us': np.float64(3.604), 'max_duration_us': np.float64(5.968)}, {'name': 'void at::native::(anonymous namespace)::ComputeInternalGradientsCUDAKernel&lt;float&gt;(long, float const*, float const*, at::AccumulateType&lt;float, true&gt;::type*, at::AccumulateType&lt;float, true&gt;::type*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(14.658999999999999), 'mean_duration_us': np.float64(4.886333333333333), 'median_duration_us': np.float64(4.446), 'std_dev_duration_us': np.float64(0.9517430792440201), 'min_duration_us': np.float64(4.005), 'max_duration_us': np.float64(6.208)}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.89)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(4.54)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(4.58)}, {'name': 'void at::native::(anonymous namespace)::ComputeBackwardFusedPara...', 'stream': 0, 'mean_duration_us': np.float64(4.54)}, {'name': 'void at::native::(anonymous namespace)::ComputeInternalGradients...', 'stream': 0, 'mean_duration_us': np.float64(4.89)}]</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -6487,12 +7211,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.575), 'mean_duration_us': np.float64(3.858333333333333), 'median_duration_us': np.float64(4.045), 'std_dev_duration_us': np.float64(0.6352187724625972), 'min_duration_us': np.float64(3.004), 'max_duration_us': np.float64(4.526)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.09), 'mean_duration_us': np.float64(3.03), 'median_duration_us': np.float64(3.124), 'std_dev_duration_us': np.float64(0.7386600481051259), 'min_duration_us': np.float64(2.082), 'max_duration_us': np.float64(3.884)}, {'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.056999999999999), 'mean_duration_us': np.float64(4.352333333333333), 'median_duration_us': np.float64(4.165), 'std_dev_duration_us': np.float64(0.4455418673430763), 'min_duration_us': np.float64(3.925), 'max_duration_us': np.float64(4.967)}]</t>
+          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(13.056999999999999), 'mean_duration_us': np.float64(4.352333333333333), 'median_duration_us': np.float64(4.165), 'std_dev_duration_us': np.float64(0.4455418673430763), 'min_duration_us': np.float64(3.925), 'max_duration_us': np.float64(4.967)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(9.09), 'mean_duration_us': np.float64(3.03), 'median_duration_us': np.float64(3.124), 'std_dev_duration_us': np.float64(0.7386600481051259), 'min_duration_us': np.float64(2.082), 'max_duration_us': np.float64(3.884)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.575), 'mean_duration_us': np.float64(3.858333333333333), 'median_duration_us': np.float64(4.045), 'std_dev_duration_us': np.float64(0.6352187724625972), 'min_duration_us': np.float64(3.004), 'max_duration_us': np.float64(4.526)}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.86)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.03)}, {'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'mean_duration_us': np.float64(4.35)}]</t>
+          <t>[{'name': 'MIOpenBatchNormFwdTrainSpatial', 'stream': 0, 'mean_duration_us': np.float64(4.35)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.03)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.86)}]</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6644,12 +7368,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.149), 'mean_duration_us': np.float64(7.049666666666667), 'median_duration_us': np.float64(6.809), 'std_dev_duration_us': np.float64(0.4280197295556465), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(7.651)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.736), 'mean_duration_us': np.float64(3.9120000000000004), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.0972787552243353), 'min_duration_us': np.float64(2.363), 'max_duration_us': np.float64(4.767)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::(anonymous namespace)::GroupNormKernelImplInternal&lt;float&gt;(at::Tensor const&amp;, at::Tensor const&amp;, at::Tensor const&amp;, long, long, long, long, float, at::Tensor&amp;, at::Tensor&amp;, at::Tensor&amp;)::{lambda(float, float, float)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(11.736), 'mean_duration_us': np.float64(3.9120000000000004), 'median_duration_us': np.float64(4.606), 'std_dev_duration_us': np.float64(1.0972787552243353), 'min_duration_us': np.float64(2.363), 'max_duration_us': np.float64(4.767)}, {'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel&lt;float&gt;(long, float, float const*, float*, float*)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.149), 'mean_duration_us': np.float64(7.049666666666667), 'median_duration_us': np.float64(6.809), 'std_dev_duration_us': np.float64(0.4280197295556465), 'min_duration_us': np.float64(6.689), 'max_duration_us': np.float64(7.651)}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.05)}, {'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.91)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(3.91)}, {'name': 'void at::native::(anonymous namespace)::RowwiseMomentsCUDAKernel...', 'stream': 0, 'mean_duration_us': np.float64(7.05)}]</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -8870,102 +9594,102 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>process_name</t>
+          <t>param: op_shape</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
+          <t>param: dtype_in_out</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>thread_name</t>
+          <t>param: stride_input</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -9052,77 +9776,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>(8, 16)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>('float', 'float')</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(16, 1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.28e-07</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0009765625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0003172617769375312</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0002957212386351248</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9.634005023826169e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0002262543963750135</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.000491827392120075</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.96577221171914e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.69651548293906e-05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.204250627978271e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.828179954687669e-05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.147842401500938e-05</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(8, 16)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>('float', 'float')</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(16, 1)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(0, 1)</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1.28e-07</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0009765625</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0003172617769375312</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.0002957212386351248</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9.634005023826169e-05</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0002262543963750135</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.000491827392120075</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.96577221171914e-05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.69651548293906e-05</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.204250627978271e-05</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.828179954687669e-05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>6.147842401500938e-05</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -9206,112 +9930,112 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>process_name</t>
+          <t>param: shape_in1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
+          <t>param: shape_in2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>thread_name</t>
+          <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: stride_input1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: stride_input2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -9398,87 +10122,87 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>(16,)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(16,)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('float', 'float', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(1,)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(1,)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.6e-08</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.00018310546875</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001020163951277465</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001009906255499077</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.268934582028177e-06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.786361373817821e-05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0001090146936512337</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.501366260645541e-06</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.415885462492306e-06</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.557445485023487e-07</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8.155301144848183e-06</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9.084557804269476e-06</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(16,)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(16,)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>('float', 'float', None)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.6e-08</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.00018310546875</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0001020163951277465</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0001009906255499077</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.268934582028177e-06</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>9.786361373817821e-05</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.0001090146936512337</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8.501366260645541e-06</v>
-      </c>
-      <c r="T2" t="n">
-        <v>8.415885462492306e-06</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.557445485023487e-07</v>
-      </c>
-      <c r="V2" t="n">
-        <v>8.155301144848183e-06</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9.084557804269476e-06</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -9548,87 +10272,87 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('long int', 'long int', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.288818359375e-05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.159373148075394e-06</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.712597892214445e-06</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.242418453072257e-06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.211748489025555e-06</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.275350285417748e-05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.399738811698081e-07</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.796915788422685e-07</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.351007688780107e-07</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.171561870427314e-07</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.313959522573949e-07</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>('long int', 'long int', None)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1e-09</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.288818359375e-05</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.04166666666666666</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8.159373148075394e-06</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.712597892214445e-06</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.242418453072257e-06</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.211748489025555e-06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.275350285417748e-05</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.399738811698081e-07</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.796915788422685e-07</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.351007688780107e-07</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.171561870427314e-07</v>
-      </c>
-      <c r="W3" t="n">
-        <v>5.313959522573949e-07</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
@@ -9694,87 +10418,87 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>(16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('float', 'float', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.6384e-05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04795802613051017</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0480332236803435</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.003386136466877823</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04463509411373463</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05113056304761905</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.003996502177542514</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.004002768640028624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0002821780389064852</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.003719591176144552</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.004260880253968253</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>('float', 'float', None)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>(1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>1.6384e-05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.04795802613051017</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0480332236803435</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.003386136466877823</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.04463509411373463</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.05113056304761905</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.003996502177542514</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.004002768640028624</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.0002821780389064852</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.003719591176144552</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.004260880253968253</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -9844,87 +10568,87 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>(32, 32)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(32, 32)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('float', 'float', None)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(32, 1)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(32, 1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.024e-06</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01171875</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.005466037708706859</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.005466037708706859</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0006164429592976079</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005030146711972817</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0059019287054409</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0004555031423922382</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0004555031423922382</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.137024660813406e-05</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0004191788926644014</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.000491827392120075</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(32, 32)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(32, 32)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>('float', 'float', None)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(32, 1)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>(32, 1)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.024e-06</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.01171875</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.005466037708706859</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.005466037708706859</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0006164429592976079</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.005030146711972817</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.0059019287054409</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0004555031423922382</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0004555031423922382</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5.137024660813406e-05</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.0004191788926644014</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.000491827392120075</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -9994,17 +10718,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>(1,)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>thread 2300490 (python)</t>
+          <t>('long int', 'Scalar', None)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10019,33 +10743,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>('long int', 'Scalar', None)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="H6" t="n">
         <v>1e-09</v>
       </c>
-      <c r="L6" t="n">
+      <c r="I6" t="n">
         <v>1.9073486328125e-05</v>
       </c>
-      <c r="M6" t="n">
+      <c r="J6" t="n">
         <v>0.05</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -10053,9 +10765,21 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>thread 2300490 (python)</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
@@ -10116,17 +10840,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>(1,)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>thread 2300490 (python)</t>
+          <t>('long int', 'long int', None)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10141,33 +10865,21 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>('long int', 'long int', None)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(1,)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="H7" t="n">
         <v>1e-09</v>
       </c>
-      <c r="L7" t="n">
+      <c r="I7" t="n">
         <v>2.288818359375e-05</v>
       </c>
-      <c r="M7" t="n">
+      <c r="J7" t="n">
         <v>0.04166666666666666</v>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -10175,9 +10887,21 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>thread 2300490 (python)</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
@@ -10252,127 +10976,127 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>process_name</t>
+          <t>param: op_shape</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
+          <t>param: dtype_in_out</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>thread_name</t>
+          <t>param: stride_input</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>param: num_channels</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>param: has_bias</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>param: is_affine</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>param: num_channels</t>
+          <t>param: is_training</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>param: has_bias</t>
+          <t>param: output_mask</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>param: is_affine</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>param: is_training</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>param: output_mask</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -10459,102 +11183,102 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.06029117081479473</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06186871052394456</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.01901091404536839</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02730805511770987</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.08236284476478933</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0376737050579451</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.03865945081336047</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01187921148234536</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.01706378563075202</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.05146547130314764</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.06029117081479473</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.06186871052394456</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.01901091404536839</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.02730805511770987</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.08236284476478933</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.0376737050579451</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.03865945081336047</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.01187921148234536</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.01706378563075202</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.05146547130314764</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -10624,102 +11348,102 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16384.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>[True, True, True]</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.05628963269412802</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05683579419860258</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.001008475034056347</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.05512587657870418</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0569072273050773</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.03618619244622515</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03653729627053023</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.0006483053790362222</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.03543806351488125</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03658321755326398</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16384.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>[True, True, True]</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.05628963269412802</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.05683579419860258</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.001008475034056347</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.05512587657870418</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.0569072273050773</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.03618619244622515</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.03653729627053023</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.0006483053790362222</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.03543806351488125</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.03658321755326398</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -10789,102 +11513,102 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.07847361405809597</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07186558594633613</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.02181711774215055</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05680999814888272</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1133891101023963</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04903523602049969</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.04490612559300802</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01363270356047803</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.03549845003305566</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.07085262788979203</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.07847361405809597</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.07186558594633613</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.02181711774215055</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.05680999814888272</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1133891101023963</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.04903523602049969</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.04490612559300802</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.01363270356047803</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.03549845003305566</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.07085262788979203</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -10954,102 +11678,102 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16384.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000753664</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1057710683031978</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1083376318348772</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.01319441490156889</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.082553959293223</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1176222919056724</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.05528942206758067</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05663103482277673</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.006897080516729191</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04315320599418475</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.0614843798597833</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16384.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0.000753664</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.5227272727272727</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1057710683031978</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1083376318348772</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.01319441490156889</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.082553959293223</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1176222919056724</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.05528942206758067</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.05663103482277673</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.006897080516729191</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.04315320599418475</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0614843798597833</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -11119,102 +11843,102 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16384.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.000753664</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1057710683031978</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1083376318348772</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.01319441490156889</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.082553959293223</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1176222919056724</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.05528942206758067</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05663103482277673</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.006897080516729191</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04315320599418475</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0614843798597833</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>16384.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.000753664</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.5227272727272727</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.1057710683031978</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1083376318348772</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.01319441490156889</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.082553959293223</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1176222919056724</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.05528942206758067</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.05663103482277673</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.006897080516729191</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.04315320599418475</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.0614843798597833</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -11284,102 +12008,102 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08244925142955863</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.08380426443270807</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.02125372186575851</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05768561746462232</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1158846736433272</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.05151946360682275</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.05236616071919339</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01328065848005892</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.03604559190139899</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0724120125148344</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.08244925142955863</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.08380426443270807</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.02125372186575851</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.05768561746462232</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1158846736433272</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.05151946360682275</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.05236616071919339</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.01328065848005892</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.03604559190139899</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.0724120125148344</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -11449,102 +12173,102 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.08244925142955863</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08380426443270807</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.02125372186575851</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05768561746462232</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1158846736433272</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.05151946360682275</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.05236616071919339</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.01328065848005892</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.03604559190139899</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0724120125148344</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.08244925142955863</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.08380426443270807</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.02125372186575851</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.05768561746462232</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.1158846736433272</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.05151946360682275</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.05236616071919339</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.01328065848005892</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.03604559190139899</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.0724120125148344</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -11614,102 +12338,102 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16384.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[True, False, False]</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.5625</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.06680599771272798</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06661193893554086</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.00219379562352543</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.06471567821944493</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.06909037598319813</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.04810031835316414</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.04796059603358942</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.001579532848938307</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.04659528831800035</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04974507070790265</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>16384.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>[True, False, False]</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.5625</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.06680599771272798</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.06661193893554086</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.00219379562352543</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.06471567821944493</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.06909037598319813</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.04810031835316414</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.04796059603358942</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.001579532848938307</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.04659528831800035</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.04974507070790265</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -11779,102 +12503,102 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06114965934906944</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0737780781647091</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.02962035089441791</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.02730805511770987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.08236284476478933</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.03821014253956648</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.04610117068479978</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01850865306193904</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.01706378563075202</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.05146547130314764</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.06114965934906944</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.0737780781647091</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.02962035089441791</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.02730805511770987</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.08236284476478933</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.03821014253956648</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.04610117068479978</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.01850865306193904</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.01706378563075202</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.05146547130314764</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -11944,102 +12668,102 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>(1, 128, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(131072, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.000656128</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.0029296875</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.623904576436222</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1528552967558544</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1386079341065403</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1016204193338914</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05695557593547534</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2679491296342374</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.09536711917849433</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.0864781244194408</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.06340144468178278</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.03553484447970382</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1671746882309032</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(1, 128, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>(131072, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0.000656128</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.0029296875</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.623904576436222</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.1528552967558544</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1386079341065403</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1016204193338914</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.05695557593547534</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.2679491296342374</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.09536711917849433</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.0864781244194408</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.06340144468178278</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.03553484447970382</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.1671746882309032</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -12109,102 +12833,102 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[True, True, True]</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.50006103515625</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.749969483663588</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.08158110778877121</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07823573877352762</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.008789629375982646</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.07495536086744072</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0915522237253453</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.06118334128504826</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.05867441661202185</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.006591953804700008</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.05621423328757242</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0686613739555505</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>[True, True, True]</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.50006103515625</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.749969483663588</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.08158110778877121</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.07823573877352762</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.008789629375982646</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.07495536086744072</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.0915522237253453</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.06118334128504826</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.05867441661202185</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.006591953804700008</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.05621423328757242</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.0686613739555505</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -12274,102 +12998,102 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.000655456</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.0003662109375</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.624862721171446</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.05943268228052002</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05938713108862719</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.004894991042083343</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.05456062579367095</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.06435028995926192</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.03713726757632372</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.03710880433460496</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.003058697422666048</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.03409290110225022</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.04021009729211598</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>0.000655456</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.0003662109375</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.624862721171446</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.05943268228052002</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.05938713108862719</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.004894991042083343</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.05456062579367095</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.06435028995926192</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.03713726757632372</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.03710880433460496</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.003058697422666048</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.03409290110225022</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.04021009729211598</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -12439,102 +13163,102 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>(1, 128, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(131072, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.000656128</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.0029296875</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.623904576436222</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.06165094775847439</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06251705622478303</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.004327812281425612</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.05695557593547534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.06548021111516479</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.03846430844814261</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.03900467748396273</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.002700141888338324</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.03553484447970382</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.04085340338076128</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(1, 128, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>(131072, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>0.000656128</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.0029296875</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.623904576436222</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.06165094775847439</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.06251705622478303</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.004327812281425612</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.05695557593547534</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.06548021111516479</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.03846430844814261</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.03900467748396273</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.002700141888338324</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.03553484447970382</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.04085340338076128</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -12604,102 +13328,102 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[True, True]</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.00131072</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.5078125</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8290155440414507</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.09662045428134391</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.09795210357866714</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.005130784259081977</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09095513168539326</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1009541275799713</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.08009985847158045</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.08120381643827329</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.004253499903902161</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.07540321797752809</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.08369254099893997</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>[True, True]</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>0.00131072</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.5078125</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.8290155440414507</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.09662045428134391</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.09795210357866714</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.005130784259081977</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.09095513168539326</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1009541275799713</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.08009985847158045</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.08120381643827329</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.004253499903902161</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.07540321797752809</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.08369254099893997</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -12769,102 +13493,102 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[True, False, False]</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.50006103515625</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.749969483663588</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1160727043946573</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1204695790575916</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.02471211817896858</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.08945727697861705</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1382912571477634</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.08705098618229744</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.09034850800299177</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01853333451091463</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.06709022782560399</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1037142227182966</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>[True, False, False]</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.50006103515625</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.749969483663588</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1160727043946573</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1204695790575916</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.02471211817896858</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.08945727697861705</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.1382912571477634</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.08705098618229744</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.09034850800299177</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.01853333451091463</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.06709022782560399</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.1037142227182966</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -12934,102 +13658,102 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[True]</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.500244140625</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7498779495524817</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.13861462663244</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.138284391793287</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.001021216688976221</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1377993909324209</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.139760097171612</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1039440519971169</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1036964161730621</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.0007657878767782663</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1033327247219846</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.104803015096304</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>[True]</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.500244140625</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.7498779495524817</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.13861462663244</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.138284391793287</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.001021216688976221</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.1377993909324209</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.139760097171612</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.1039440519971169</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1036964161730621</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.0007657878767782663</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.1033327247219846</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.104803015096304</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -13099,102 +13823,102 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0005245440000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.00390625</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4982976653696498</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2345369704960928</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2479439085124426</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.02585868594391625</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1904312566027736</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2551328113609468</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1168692248410735</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1235498707543762</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.01288532283538044</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.09489145057857082</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.127132084260355</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>0.0005245440000000001</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.00390625</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.4982976653696498</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.2345369704960928</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2479439085124426</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.02585868594391625</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.1904312566027736</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.2551328113609468</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.1168692248410735</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1235498707543762</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.01288532283538044</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.09489145057857082</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.127132084260355</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -13264,102 +13988,102 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>(1, 128, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(131072, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[True]</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.001179648</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.501953125</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7490247074122237</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.241821376849506</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2488365820089493</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0297823893140027</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2091576276506063</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2674699208889626</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1811301860407223</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.186384748032711</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.0223077454419578</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.1566642308540302</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2003415792354258</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>(1, 128, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>(131072, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>[True]</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>0.001179648</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.501953125</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7490247074122237</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.241821376849506</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2488365820089493</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.0297823893140027</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.2091576276506063</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.2674699208889626</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.1811301860407223</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.186384748032711</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.0223077454419578</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.1566642308540302</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.2003415792354258</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -13429,102 +14153,102 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[True, False]</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.001048576</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.5078125</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6632124352331606</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2734392754403918</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.2881554407760079</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.03747419808787525</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2308407134811435</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3013216720640238</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1813483277532132</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1911082716027409</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.0248533541722696</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1530964317387895</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.199840279918109</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>[True, False]</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>0.001048576</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.5078125</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.6632124352331606</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.2734392754403918</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2881554407760079</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.03747419808787525</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.2308407134811435</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3013216720640238</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.1813483277532132</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1911082716027409</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.0248533541722696</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.1530964317387895</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.199840279918109</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -13594,102 +14318,102 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>(8, 16, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(16384, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[True]</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.000524336</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.00006103515625</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5000152578577968</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2067490101745708</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2094416539886874</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.01852446773236728</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1870255786815292</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2237797978534959</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1033776596342823</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.104724022625317</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.00926251650987806</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.09351564295044849</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.1118933133270814</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>(8, 16, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>(16384, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>[True]</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>0.000524336</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.00006103515625</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.5000152578577968</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2067490101745708</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.2094416539886874</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.01852446773236728</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.1870255786815292</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.2237797978534959</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.1033776596342823</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.104724022625317</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.00926251650987806</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.09351564295044849</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.1118933133270814</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -13759,102 +14483,102 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>(1, 128, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>(131072, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[True]</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.000524672</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.00048828125</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5001220107369448</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.2371125493316399</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2447632973342447</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.02942084384243977</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2046221165714285</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2619522340892465</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1185852049427028</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1224115124174072</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.01471401158005863</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1023360243809524</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1310080780297488</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>thread 2300680 (pt_autograd_0)</t>
         </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>(1, 128, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>(131072, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>[True]</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>0.000524672</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.00048828125</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.5001220107369448</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.2371125493316399</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2447632973342447</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.02942084384243977</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.2046221165714285</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.2619522340892465</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.1185852049427028</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1224115124174072</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.01471401158005863</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.1023360243809524</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.1310080780297488</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -13924,102 +14648,102 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>(1, 128, 32, 32)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>('float', None)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>(131072, 1024, 32, 1)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.000656128</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.0029296875</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.623904576436222</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.2440596457532344</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2524941505275499</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.02904039043709479</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2117356570979159</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2679491296342374</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1522699299088461</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1575322560375147</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.01811843249519814</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1321028454581203</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1671746882309032</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>thread 2300490 (python)</t>
         </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>(1, 128, 32, 32)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>('float', None)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>(131072, 1024, 32, 1)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>0.000656128</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.0029296875</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.623904576436222</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.2440596457532344</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.2524941505275499</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.02904039043709479</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2117356570979159</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.2679491296342374</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.1522699299088461</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.1575322560375147</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.01811843249519814</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.1321028454581203</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.1671746882309032</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
